--- a/test/G14-G24.xlsx
+++ b/test/G14-G24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B971552E-977C-44E5-8220-C4EA166C1A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA6CB5D-99C3-4161-B6DD-3B762DC0F579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Python, MIDPTS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="82">
   <si>
     <t>SACOBRA_Py, 10 runs, mean(time), median(err)</t>
   </si>
@@ -262,22 +262,6 @@
     <t>muFinal=1e-7</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">TGR=np.inf, muFinal=1e-7, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>epsilonMax=0.0</t>
-    </r>
-  </si>
-  <si>
     <t>NaN</t>
   </si>
   <si>
@@ -288,22 +272,6 @@
   </si>
   <si>
     <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPSNone.feather from 18.09.2025</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TGR=1e3, muFinal=1e-7, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>epsilonMax=None</t>
-    </r>
   </si>
   <si>
     <t>7 infeasible</t>
@@ -397,6 +365,54 @@
   </si>
   <si>
     <t>better than trueFunc</t>
+  </si>
+  <si>
+    <r>
+      <t>ISA.TGR=1e3, muFinal=1e-7, SEQ.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>epsilonMax=None</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ISA.TGR=1e3, muFinal=1e-7,  SEQ.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>epsilonMax=None</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ISA.TGR=np.inf, muFinal=1e-7,  SEQ.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>epsilonMax=0.0</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1977,7 +1993,7 @@
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -2139,7 +2155,7 @@
     </row>
     <row r="2" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="3:21" x14ac:dyDescent="0.3">
@@ -2190,7 +2206,7 @@
         <v>21</v>
       </c>
       <c r="T4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="U4" t="s">
         <v>33</v>
@@ -2401,10 +2417,10 @@
         <v>2620.81477</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -2569,13 +2585,13 @@
         <v>2620.81477</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M13" t="s">
         <v>30</v>
@@ -2593,10 +2609,10 @@
         <v>6047.4524350000002</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -2782,7 +2798,7 @@
         <v>33</v>
       </c>
       <c r="R18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="3:21" x14ac:dyDescent="0.3">
@@ -2873,13 +2889,13 @@
         <v>6047.4524350000002</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M21" t="s">
         <v>24</v>
@@ -2958,7 +2974,7 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M23" t="s">
         <v>26</v>
@@ -2970,7 +2986,7 @@
         <v>6</v>
       </c>
       <c r="P23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q23">
         <v>6.8633569999999997</v>
@@ -3091,7 +3107,7 @@
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -3103,7 +3119,7 @@
         <v>22</v>
       </c>
       <c r="P27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q27">
         <v>9.5238270000000007</v>
@@ -3160,22 +3176,22 @@
         <v>2</v>
       </c>
       <c r="O31" t="s">
+        <v>49</v>
+      </c>
+      <c r="P31" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q31" t="s">
         <v>51</v>
       </c>
-      <c r="P31" t="s">
+      <c r="R31" t="s">
         <v>52</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="S31" t="s">
         <v>53</v>
       </c>
-      <c r="R31" t="s">
+      <c r="T31" t="s">
         <v>54</v>
-      </c>
-      <c r="S31" t="s">
-        <v>55</v>
-      </c>
-      <c r="T31" t="s">
-        <v>56</v>
       </c>
       <c r="U31" t="s">
         <v>2</v>
@@ -3364,7 +3380,7 @@
     </row>
     <row r="2" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="3:21" x14ac:dyDescent="0.3">
@@ -3754,7 +3770,7 @@
       </c>
       <c r="J12" s="25"/>
       <c r="K12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M12" t="s">
         <v>29</v>
@@ -4070,7 +4086,7 @@
       </c>
       <c r="J20" s="25"/>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -4112,7 +4128,7 @@
         <v>5.1004160000000001</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M21" t="s">
         <v>24</v>
@@ -4146,16 +4162,16 @@
         <v>16759.19471</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I22" s="33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J22" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M22" t="s">
         <v>25</v>
@@ -4198,7 +4214,7 @@
       </c>
       <c r="J23" s="23"/>
       <c r="K23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M23" t="s">
         <v>26</v>
@@ -4323,7 +4339,7 @@
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -4435,7 +4451,7 @@
     </row>
     <row r="36" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M36" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="13:21" x14ac:dyDescent="0.3">
@@ -4475,7 +4491,7 @@
         <v>21</v>
       </c>
       <c r="T38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U38" t="s">
         <v>33</v>
@@ -4567,10 +4583,10 @@
         <v>16759.19471</v>
       </c>
       <c r="R42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T42">
         <v>10</v>
@@ -4581,7 +4597,7 @@
     </row>
     <row r="44" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M44" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="13:21" x14ac:dyDescent="0.3">
@@ -4621,7 +4637,7 @@
         <v>21</v>
       </c>
       <c r="T46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U46" t="s">
         <v>33</v>
@@ -4669,7 +4685,7 @@
     </row>
     <row r="51" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M51" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="13:21" x14ac:dyDescent="0.3">
@@ -4709,7 +4725,7 @@
         <v>21</v>
       </c>
       <c r="T53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U53" t="s">
         <v>33</v>
@@ -4801,10 +4817,10 @@
         <v>16661.278170000001</v>
       </c>
       <c r="R57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T57">
         <v>10</v>
@@ -4815,7 +4831,7 @@
     </row>
     <row r="59" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M59" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="13:21" x14ac:dyDescent="0.3">
@@ -4856,12 +4872,12 @@
     </row>
     <row r="2" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
         <v>2</v>
@@ -4901,10 +4917,10 @@
         <v>8</v>
       </c>
       <c r="R4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="S4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="3:19" x14ac:dyDescent="0.3">
@@ -5249,7 +5265,7 @@
         <v>11605.569545</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R13" s="64">
         <v>0</v>
@@ -5380,7 +5396,7 @@
       </c>
       <c r="J17" s="30"/>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M17" t="s">
         <v>2</v>
@@ -5426,10 +5442,10 @@
         <v>33</v>
       </c>
       <c r="R18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="S18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
@@ -5516,16 +5532,16 @@
         <v>11605.569545</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M21" t="s">
         <v>24</v>
@@ -5604,7 +5620,7 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M23" t="s">
         <v>26</v>
@@ -5749,7 +5765,7 @@
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -5761,7 +5777,7 @@
         <v>22</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q27" s="6">
         <v>316361500</v>
@@ -5824,7 +5840,7 @@
     </row>
     <row r="32" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M32" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="13:22" x14ac:dyDescent="0.3">
@@ -5861,13 +5877,13 @@
         <v>21</v>
       </c>
       <c r="T34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U34" t="s">
         <v>33</v>
       </c>
       <c r="V34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="13:22" x14ac:dyDescent="0.3">
@@ -5878,10 +5894,10 @@
         <v>10</v>
       </c>
       <c r="O35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="13:22" x14ac:dyDescent="0.3">
@@ -5895,7 +5911,7 @@
         <v>1E-4</v>
       </c>
       <c r="P36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q36">
         <v>11497.557994999999</v>
@@ -5927,7 +5943,7 @@
         <v>1E-4</v>
       </c>
       <c r="P37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q37">
         <v>9021.6708450000006</v>
@@ -5959,16 +5975,16 @@
         <v>1E-4</v>
       </c>
       <c r="P38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q38">
         <v>16759.19471</v>
       </c>
       <c r="R38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T38">
         <v>4</v>
@@ -5991,16 +6007,16 @@
         <v>1E-4</v>
       </c>
       <c r="P39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q39">
         <v>16759.19471</v>
       </c>
       <c r="R39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T39">
         <v>6</v>
@@ -6023,7 +6039,7 @@
         <v>1E-4</v>
       </c>
       <c r="P40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q40">
         <v>9735.7064549999996</v>
